--- a/src/nodes/HPC/compressor_stage_5_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_5_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.5989749834577074</v>
+        <v>4.4957998822681109</v>
       </c>
       <c r="B1">
-        <v>8.2894179361344289</v>
+        <v>8.3458255455631836</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.006018610344225</v>
+        <v>3.9051205388311518</v>
       </c>
       <c r="B2">
-        <v>8.10952220898807</v>
+        <v>8.1585886733977535</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.4786644739536396</v>
+        <v>3.3807092374073253</v>
       </c>
       <c r="B3">
-        <v>7.8755426067809386</v>
+        <v>7.918085811967301</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2.9693183715074354</v>
+        <v>2.8744887357124922</v>
       </c>
       <c r="B4">
-        <v>7.6267167995266867</v>
+        <v>7.6629612578830235</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.4750855555262055</v>
+        <v>2.3835349071136984</v>
       </c>
       <c r="B5">
-        <v>7.3654312784309388</v>
+        <v>7.3955654125316048</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.994652796582076</v>
+        <v>1.9065211940536637</v>
       </c>
       <c r="B6">
-        <v>7.0927686976812847</v>
+        <v>7.1169645576147387</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.5271951931815877</v>
+        <v>1.4426143230106925</v>
       </c>
       <c r="B7">
-        <v>6.8094091235611067</v>
+        <v>6.8278284750833178</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1.0721529578374616</v>
+        <v>0.991248825144413</v>
       </c>
       <c r="B8">
-        <v>6.5158140567453042</v>
+        <v>6.5286116865478485</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.62879064555460473</v>
+        <v>0.55168179133666462</v>
       </c>
       <c r="B9">
-        <v>6.212589813683068</v>
+        <v>6.2199113394101664</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>0.19634024548073181</v>
+        <v>0.12313741609714475</v>
       </c>
       <c r="B10">
-        <v>5.900369558806819</v>
+        <v>5.9023510230455241</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.22592085915739943</v>
+        <v>-0.29511425127523194</v>
       </c>
       <c r="B11">
-        <v>5.5797490327076291</v>
+        <v>5.57651746893152</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.63843287693997419</v>
+        <v>-0.70351788709248575</v>
       </c>
       <c r="B12">
-        <v>5.2510911526736992</v>
+        <v>5.2427681061235942</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.0405517777540008</v>
+        <v>-1.1014229248996081</v>
       </c>
       <c r="B13">
-        <v>4.9138649666231107</v>
+        <v>4.9005800118862</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.4319269585355539</v>
+        <v>-1.488475203318409</v>
       </c>
       <c r="B14">
-        <v>4.5677814299553718</v>
+        <v>4.5496685127086174</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.8144657631101673</v>
+        <v>-1.8666014240450193</v>
       </c>
       <c r="B15">
-        <v>4.2144129973657929</v>
+        <v>4.1915822837703889</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.1899167622569737</v>
+        <v>-2.2375679043216983</v>
       </c>
       <c r="B16">
-        <v>3.8552012276834295</v>
+        <v>3.8277410838633394</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.5571354876800729</v>
+        <v>-2.600218560500938</v>
       </c>
       <c r="B17">
-        <v>3.4892025969764981</v>
+        <v>3.457215657538125</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.9146168587222259</v>
+        <v>-2.9530330366740145</v>
       </c>
       <c r="B18">
-        <v>3.1151762848356817</v>
+        <v>3.0787839487470223</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.2623063843558842</v>
+        <v>-3.295956288777139</v>
       </c>
       <c r="B19">
-        <v>2.7330773677023865</v>
+        <v>2.6924017132899394</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.6005122209609319</v>
+        <v>-3.629299600707764</v>
       </c>
       <c r="B20">
-        <v>2.3431598962306879</v>
+        <v>2.2983191599286856</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.9295425249172444</v>
+        <v>-3.9533742563633343</v>
       </c>
       <c r="B21">
-        <v>1.9456779210746651</v>
+        <v>1.8967864974250732</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.2496472588899605</v>
+        <v>-4.2684327553112835</v>
       </c>
       <c r="B22">
-        <v>1.5408375167559596</v>
+        <v>1.4880066839296644</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.5608436106852546</v>
+        <v>-4.5744924597989742</v>
       </c>
       <c r="B23">
-        <v>1.128652853266451</v>
+        <v>1.0719936751480081</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-4.8630905743945627</v>
+        <v>-4.8715119477437625</v>
       </c>
       <c r="B24">
-        <v>0.70909012446558228</v>
+        <v>0.6487141761744053</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.1563471441093185</v>
+        <v>-5.1594497970629911</v>
       </c>
       <c r="B25">
-        <v>0.282115524212795</v>
+        <v>0.2181348921031557</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-5.440556501111228</v>
+        <v>-5.4382486123781026</v>
       </c>
       <c r="B26">
-        <v>-0.15231779004812102</v>
+        <v>-0.21979031124332071</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-5.715598575443086</v>
+        <v>-5.7077871051269078</v>
       </c>
       <c r="B27">
-        <v>-0.59430880653599383</v>
+        <v>-0.66515892513012909</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-5.9813374843379536</v>
+        <v>-5.967928013451302</v>
       </c>
       <c r="B28">
-        <v>-1.0439695498853023</v>
+        <v>-1.1180812800942515</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.2376373450288947</v>
+        <v>-6.218534075493185</v>
       </c>
       <c r="B29">
-        <v>-1.5014120447305255</v>
+        <v>-1.5786677066726711</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.4843915478894569</v>
+        <v>-6.4594975996316952</v>
       </c>
       <c r="B30">
-        <v>-1.9667241823083876</v>
+        <v>-2.0470047669629943</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-6.7216105758551077</v>
+        <v>-6.69082917519492</v>
       </c>
       <c r="B31">
-        <v>-2.4398973202645897</v>
+        <v>-2.5230839493053043</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-6.9493341850018089</v>
+        <v>-6.9125689617482</v>
       </c>
       <c r="B32">
-        <v>-2.9208986828470871</v>
+        <v>-3.0068729736003204</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.1676021314055056</v>
+        <v>-7.1247571188568575</v>
       </c>
       <c r="B33">
-        <v>-3.4096954943038233</v>
+        <v>-3.4983395597487488</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-7.3763814341497724</v>
+        <v>-7.3273603308770321</v>
       </c>
       <c r="B34">
-        <v>-3.906314944801677</v>
+        <v>-3.9975104867329638</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-7.57534816434862</v>
+        <v>-7.5200513813280283</v>
       </c>
       <c r="B35">
-        <v>-4.4110240881832175</v>
+        <v>-4.5046487698619746</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-7.764105656123677</v>
+        <v>-7.7024295785199568</v>
       </c>
       <c r="B36">
-        <v>-4.9241499442099368</v>
+        <v>-5.0200764835264478</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-7.942257243596571</v>
+        <v>-7.8740942307629274</v>
       </c>
       <c r="B37">
-        <v>-5.4460195326433354</v>
+        <v>-5.5441157021170584</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.1092423367931374</v>
+        <v>-8.0344790585851431</v>
       </c>
       <c r="B38">
-        <v>-5.9770950157455243</v>
+        <v>-6.0772215988266405</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-8.2638446493560256</v>
+        <v>-8.1823554313871671</v>
       </c>
       <c r="B39">
-        <v>-6.5183791257810517</v>
+        <v>-6.6203817420566669</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-8.4046839708320871</v>
+        <v>-8.3163291307876683</v>
       </c>
       <c r="B40">
-        <v>-7.0710097375150918</v>
+        <v>-7.1747167990107821</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-8.53038009076818</v>
+        <v>-8.4350059384053022</v>
       </c>
       <c r="B41">
-        <v>-7.6361247257128042</v>
+        <v>-7.7413474368926165</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-8.53038009076818</v>
+        <v>-8.4350059384053022</v>
       </c>
       <c r="B42">
-        <v>-7.6361247257128042</v>
+        <v>-7.7413474368926165</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-8.3522625289342631</v>
+        <v>-8.2633756571317676</v>
       </c>
       <c r="B43">
-        <v>-7.1142270858211125</v>
+        <v>-7.217280591053135</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.1680047336170283</v>
+        <v>-8.08554282437875</v>
       </c>
       <c r="B44">
-        <v>-6.5973915846177436</v>
+        <v>-6.6981993314854789</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-7.9767682283869172</v>
+        <v>-7.9006604539147327</v>
       </c>
       <c r="B45">
-        <v>-6.0863094798512662</v>
+        <v>-6.1847844623623072</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-7.777714536814365</v>
+        <v>-7.707881559508194</v>
       </c>
       <c r="B46">
-        <v>-5.5816720292702371</v>
+        <v>-5.677716787856256</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-7.5701413851788706</v>
+        <v>-7.50649673997497</v>
       </c>
       <c r="B47">
-        <v>-5.0840582022216818</v>
+        <v>-5.1775665218247635</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.3538913105961292</v>
+        <v>-7.2963469343202867</v>
       </c>
       <c r="B48">
-        <v>-4.5935978144464391</v>
+        <v>-4.6844615168643786</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.1289430528908939</v>
+        <v>-7.0774106665967249</v>
       </c>
       <c r="B49">
-        <v>-4.1103083932838063</v>
+        <v>-4.1984190352564337</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-6.8952753518879186</v>
+        <v>-6.8496664608568638</v>
       </c>
       <c r="B50">
-        <v>-3.6342074660730859</v>
+        <v>-3.7194563392822642</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-6.652916548447843</v>
+        <v>-6.6131429455962794</v>
       </c>
       <c r="B51">
-        <v>-3.1652716680077972</v>
+        <v>-3.247550417470713</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.4020933875748369</v>
+        <v>-6.368069167082492</v>
       </c>
       <c r="B52">
-        <v>-2.7033140656983292</v>
+        <v>-2.7825171633406307</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.1430822153089677</v>
+        <v>-6.1147242760260285</v>
       </c>
       <c r="B53">
-        <v>-2.2481068336092962</v>
+        <v>-2.3241321966583812</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-5.8761593776902865</v>
+        <v>-5.853387423137403</v>
       </c>
       <c r="B54">
-        <v>-1.7994221462053046</v>
+        <v>-1.872171137190316</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.6015546783619383</v>
+        <v>-5.58429074436562</v>
       </c>
       <c r="B55">
-        <v>-1.3570705484899281</v>
+        <v>-1.4264473949815866</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.3193117513793773</v>
+        <v>-5.30747831661361</v>
       </c>
       <c r="B56">
-        <v>-0.92101606762258137</v>
+        <v>-0.98692554119247977</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.0294276884011415</v>
+        <v>-5.0229472020227908</v>
       </c>
       <c r="B57">
-        <v>-0.49126110130163742</v>
+        <v>-0.55360793726206936</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.7318995810857656</v>
+        <v>-4.7306944627345784</v>
       </c>
       <c r="B58">
-        <v>-0.067808047225473456</v>
+        <v>-0.12649694462943223</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.4267254002446963</v>
+        <v>-4.4307180489659288</v>
       </c>
       <c r="B59">
-        <v>0.34934142169984039</v>
+        <v>0.29440578909795645</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.1139066333010064</v>
+        <v>-4.1230194632359582</v>
       </c>
       <c r="B60">
-        <v>0.76018853173742862</v>
+        <v>0.70910147163900317</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.793445646830687</v>
+        <v>-3.8076010961393334</v>
       </c>
       <c r="B61">
-        <v>1.1647352339427157</v>
+        <v>1.1175920245442113</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.4653448074097208</v>
+        <v>-3.484465338270712</v>
       </c>
       <c r="B62">
-        <v>1.5629834793711288</v>
+        <v>1.5198793693640846</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.1296499028029308</v>
+        <v>-3.1536584421006584</v>
       </c>
       <c r="B63">
-        <v>1.9549710164269247</v>
+        <v>1.9160006836509658</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.7865804055304859</v>
+        <v>-2.8154021076033469</v>
       </c>
       <c r="B64">
-        <v>2.3408787829096815</v>
+        <v>2.306134168964546</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.4363992093013933</v>
+        <v>-2.4699618966288566</v>
       </c>
       <c r="B65">
-        <v>2.72092351396781</v>
+        <v>2.6904932828663539</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.0793692078246551</v>
+        <v>-2.1176033710272639</v>
       </c>
       <c r="B66">
-        <v>3.0953219447497213</v>
+        <v>3.0692914829179228</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.7153783607683597</v>
+        <v>-1.7582133533553386</v>
       </c>
       <c r="B67">
-        <v>3.4639817068299461</v>
+        <v>3.4424377975393878</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.3428148916368994</v>
+        <v>-1.3901637089966075</v>
       </c>
       <c r="B68">
-        <v>3.8255740174875186</v>
+        <v>3.8086235385853255</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.9604092949665084</v>
+        <v>-1.0121720481178695</v>
       </c>
       <c r="B69">
-        <v>4.1790522694980341</v>
+        <v>4.1668179261954341</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.5697608855844728</v>
+        <v>-0.62585391719225014</v>
       </c>
       <c r="B70">
-        <v>4.5257349719188458</v>
+        <v>4.5183195302154529</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.17261245355111457</v>
+        <v>-0.23296979407396021</v>
       </c>
       <c r="B71">
-        <v>4.86705891783184</v>
+        <v>4.8645434157602621</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.23158813043214774</v>
+        <v>0.16703805416475817</v>
       </c>
       <c r="B72">
-        <v>5.2025689201352687</v>
+        <v>5.2050412793152141</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.643705321681301</v>
+        <v>0.57504285630481311</v>
       </c>
       <c r="B73">
-        <v>5.5315523035357144</v>
+        <v>5.5391112230505808</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.0635579602230341</v>
+        <v>0.99086161375770831</v>
       </c>
       <c r="B74">
-        <v>5.8541584201567014</v>
+        <v>5.866900340505782</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.4907031590141628</v>
+        <v>1.4140469445643678</v>
       </c>
       <c r="B75">
-        <v>6.170752395468126</v>
+        <v>6.188768235524627</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>1.9246967380212952</v>
+        <v>1.8441501606527895</v>
       </c>
       <c r="B76">
-        <v>6.4817004209084281</v>
+        <v>6.505075561799309</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.3651516638715453</v>
+        <v>2.2807803006000706</v>
       </c>
       <c r="B77">
-        <v>6.7873215749973212</v>
+        <v>6.8161365725705</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.8119107828242744</v>
+        <v>2.7237786156926389</v>
       </c>
       <c r="B78">
-        <v>7.08774541861106</v>
+        <v>7.1220788694243629</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.2645779324580833</v>
+        <v>3.1727449228072233</v>
       </c>
       <c r="B79">
-        <v>7.383298556450538</v>
+        <v>7.4232241179677381</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.7223252766799018</v>
+        <v>3.6268429840388987</v>
       </c>
       <c r="B80">
-        <v>7.6746634741452837</v>
+        <v>7.7202444829109966</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.18279213389073</v>
+        <v>4.0836881589364111</v>
       </c>
       <c r="B81">
-        <v>7.963786367664162</v>
+        <v>8.015056728788279</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.5989749834577074</v>
+        <v>4.4957998822681109</v>
       </c>
       <c r="B82">
-        <v>8.2894179361344289</v>
+        <v>8.3458255455631836</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.7198189463968845</v>
+        <v>4.6163197893269912</v>
       </c>
       <c r="B1">
-        <v>9.3583053126357765</v>
+        <v>9.4097906891674281</v>
       </c>
       <c r="C1">
         <v>221.20000756679073</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.0063626775182311</v>
+        <v>3.8709224579637196</v>
       </c>
       <c r="B2">
-        <v>9.1834905233247728</v>
+        <v>9.2522731412956585</v>
       </c>
       <c r="C2">
         <v>221.20000756679073</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.4095328338264288</v>
+        <v>3.2642014738441181</v>
       </c>
       <c r="B3">
-        <v>8.9201551426430665</v>
+        <v>8.9918895918476736</v>
       </c>
       <c r="C3">
         <v>221.20000756679073</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2.8390065863365583</v>
+        <v>2.6869356460897342</v>
       </c>
       <c r="B4">
-        <v>8.6368550765374437</v>
+        <v>8.70965708097753</v>
       </c>
       <c r="C4">
         <v>221.20000756679073</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.2894842316484914</v>
+        <v>2.1327730207415154</v>
       </c>
       <c r="B5">
-        <v>8.3376128514492081</v>
+        <v>8.41028729974828</v>
       </c>
       <c r="C5">
         <v>221.20000756679073</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.7586560222372767</v>
+        <v>1.5989739107594869</v>
       </c>
       <c r="B6">
-        <v>8.0241815882212428</v>
+        <v>8.0958124667536087</v>
       </c>
       <c r="C6">
         <v>221.20000756679073</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.2451191645174256</v>
+        <v>1.0838896144230024</v>
       </c>
       <c r="B7">
-        <v>7.6976260208326526</v>
+        <v>7.7674555400333265</v>
       </c>
       <c r="C7">
         <v>221.20000756679073</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.74796507989013983</v>
+        <v>0.58646646363368948</v>
       </c>
       <c r="B8">
-        <v>7.3586357692794513</v>
+        <v>7.4259980993335351</v>
       </c>
       <c r="C8">
         <v>221.20000756679073</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.26592983031256551</v>
+        <v>0.10521467892369088</v>
       </c>
       <c r="B9">
-        <v>7.0081701748329719</v>
+        <v>7.07254521888019</v>
       </c>
       <c r="C9">
         <v>221.20000756679073</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.20232206337800035</v>
+        <v>-0.36144486539143283</v>
       </c>
       <c r="B10">
-        <v>6.64724287917053</v>
+        <v>6.7082682472729136</v>
       </c>
       <c r="C10">
         <v>221.20000756679073</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.65805688537960183</v>
+        <v>-0.8150125684929258</v>
       </c>
       <c r="B11">
-        <v>6.276815004318065</v>
+        <v>6.3342801361260985</v>
       </c>
       <c r="C11">
         <v>221.20000756679073</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-1.1020116571082752</v>
+        <v>-1.2563507808212058</v>
       </c>
       <c r="B12">
-        <v>5.8974459567008033</v>
+        <v>5.95122055142119</v>
       </c>
       <c r="C12">
         <v>221.20000756679073</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.5328755438166926</v>
+        <v>-1.6838483843565391</v>
       </c>
       <c r="B13">
-        <v>5.5081407999924643</v>
+        <v>5.557894413593063</v>
       </c>
       <c r="C13">
         <v>221.20000756679073</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.9499033297493256</v>
+        <v>-2.0965807890028114</v>
       </c>
       <c r="B14">
-        <v>5.108333908184429</v>
+        <v>5.1536158891295552</v>
       </c>
       <c r="C14">
         <v>221.20000756679073</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.3566601312812</v>
+        <v>-2.4988429848185252</v>
       </c>
       <c r="B15">
-        <v>4.7007312392902119</v>
+        <v>4.7415708742769134</v>
       </c>
       <c r="C15">
         <v>221.20000756679073</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.7564149217285374</v>
+        <v>-2.894573374057368</v>
       </c>
       <c r="B16">
-        <v>4.2878139758605469</v>
+        <v>4.32468075902333</v>
       </c>
       <c r="C16">
         <v>221.20000756679073</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.1469417700418196</v>
+        <v>-3.2810644275991909</v>
       </c>
       <c r="B17">
-        <v>3.8678926145728463</v>
+        <v>3.9009371785663181</v>
       </c>
       <c r="C17">
         <v>221.20000756679073</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.5253357555024003</v>
+        <v>-3.6547891419696517</v>
       </c>
       <c r="B18">
-        <v>3.4387622923398022</v>
+        <v>3.4677239063311078</v>
       </c>
       <c r="C18">
         <v>221.20000756679073</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.8914709030808945</v>
+        <v>-4.0155885476515021</v>
       </c>
       <c r="B19">
-        <v>3.0003273928885061</v>
+        <v>3.0249230234444631</v>
       </c>
       <c r="C19">
         <v>221.20000756679073</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.24591597417023</v>
+        <v>-4.3641456836167718</v>
       </c>
       <c r="B20">
-        <v>2.5530196116496437</v>
+        <v>2.5730411879585273</v>
       </c>
       <c r="C20">
         <v>221.20000756679073</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.5892397301633343</v>
+        <v>-4.701143588837482</v>
       </c>
       <c r="B21">
-        <v>2.0972706440539093</v>
+        <v>2.1125850579254473</v>
       </c>
       <c r="C21">
         <v>221.20000756679073</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.9219059366241629</v>
+        <v>-5.0271399399731047</v>
       </c>
       <c r="B22">
-        <v>1.6334324926762966</v>
+        <v>1.6439683013518553</v>
       </c>
       <c r="C22">
         <v>221.20000756679073</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.24395837580078</v>
+        <v>-5.34219096443286</v>
       </c>
       <c r="B23">
-        <v>1.1615383886690449</v>
+        <v>1.1672326260623445</v>
       </c>
       <c r="C23">
         <v>221.20000756679073</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.5553358341122774</v>
+        <v>-5.6462275273134157</v>
       </c>
       <c r="B24">
-        <v>0.68154187032869962</v>
+        <v>0.68232674983599761</v>
       </c>
       <c r="C24">
         <v>221.20000756679073</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.8559770979777461</v>
+        <v>-5.93918049371143</v>
       </c>
       <c r="B25">
-        <v>0.19339647595180681</v>
+        <v>0.1891993904518936</v>
       </c>
       <c r="C25">
         <v>221.20000756679073</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.1457966579422481</v>
+        <v>-6.2209530287358632</v>
       </c>
       <c r="B26">
-        <v>-0.30296269696984551</v>
+        <v>-0.31222128134024724</v>
       </c>
       <c r="C26">
         <v>221.20000756679073</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.4246118210547438</v>
+        <v>-6.4913374975448539</v>
       </c>
       <c r="B27">
-        <v>-0.80767431416351676</v>
+        <v>-0.82208928290817151</v>
       </c>
       <c r="C27">
         <v>221.20000756679073</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.6922155984901615</v>
+        <v>-6.7500985653088295</v>
       </c>
       <c r="B28">
-        <v>-1.3208954821612189</v>
+        <v>-1.3405791786489825</v>
       </c>
       <c r="C28">
         <v>221.20000756679073</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.9484010014234316</v>
+        <v>-6.9970008971982214</v>
       </c>
       <c r="B29">
-        <v>-1.842783307494968</v>
+        <v>-1.8678655329597893</v>
       </c>
       <c r="C29">
         <v>221.20000756679073</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.19302344202124</v>
+        <v>-7.2318866224994709</v>
       </c>
       <c r="B30">
-        <v>-2.3734475337369338</v>
+        <v>-2.4040654496538365</v>
       </c>
       <c r="C30">
         <v>221.20000756679073</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.4261879364173131</v>
+        <v>-7.4549077269630644</v>
       </c>
       <c r="B31">
-        <v>-2.9128084526199194</v>
+        <v>-2.9490661902089457</v>
       </c>
       <c r="C31">
         <v>221.20000756679073</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.6480619017371323</v>
+        <v>-7.6662936604555023</v>
       </c>
       <c r="B32">
-        <v>-3.4607389929168977</v>
+        <v>-3.5026975555190889</v>
       </c>
       <c r="C32">
         <v>221.20000756679073</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.8588127551061788</v>
+        <v>-7.8662738728432871</v>
       </c>
       <c r="B33">
-        <v>-4.0171120834008294</v>
+        <v>-4.0647893464782276</v>
       </c>
       <c r="C33">
         <v>221.20000756679073</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.0584785349300887</v>
+        <v>-8.0549238906090146</v>
       </c>
       <c r="B34">
-        <v>-4.5818988525517614</v>
+        <v>-4.6352855397815054</v>
       </c>
       <c r="C34">
         <v>221.20000756679073</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.2465797647351273</v>
+        <v>-8.2317035466996682</v>
       </c>
       <c r="B35">
-        <v>-5.1554632276780685</v>
+        <v>-5.2145868153287855</v>
       </c>
       <c r="C35">
         <v>221.20000756679073</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.4225075893277079</v>
+        <v>-8.3959187506783248</v>
       </c>
       <c r="B36">
-        <v>-5.7382673357952045</v>
+        <v>-5.80320802882111</v>
       </c>
       <c r="C36">
         <v>221.20000756679073</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.5856531535142491</v>
+        <v>-8.5468754121080757</v>
       </c>
       <c r="B37">
-        <v>-6.3307733039186367</v>
+        <v>-6.4016640359595236</v>
       </c>
       <c r="C37">
         <v>221.20000756679073</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.7351065523837459</v>
+        <v>-8.68351831229963</v>
       </c>
       <c r="B38">
-        <v>-6.9336717587282388</v>
+        <v>-7.01073756667247</v>
       </c>
       <c r="C38">
         <v>221.20000756679073</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-8.8687536821555266</v>
+        <v>-8.8033477195542353</v>
       </c>
       <c r="B39">
-        <v>-7.54856732556158</v>
+        <v>-7.6322828477980149</v>
       </c>
       <c r="C39">
         <v>221.20000756679073</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-8.9841793893314925</v>
+        <v>-8.90350277392078</v>
       </c>
       <c r="B40">
-        <v>-8.1772931294206419</v>
+        <v>-8.268421980401623</v>
       </c>
       <c r="C40">
         <v>221.20000756679073</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.0789685204135484</v>
+        <v>-8.9811226154481449</v>
       </c>
       <c r="B41">
-        <v>-8.8216822953074114</v>
+        <v>-8.9212770655487557</v>
       </c>
       <c r="C41">
         <v>221.20000756679073</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.0789685204135484</v>
+        <v>-8.9811226154481449</v>
       </c>
       <c r="B42">
-        <v>-8.8216822953074114</v>
+        <v>-8.9212770655487557</v>
       </c>
       <c r="C42">
         <v>221.20000756679073</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-8.884442216128166</v>
+        <v>-8.7828235576914864</v>
       </c>
       <c r="B43">
-        <v>-8.2529946142209845</v>
+        <v>-8.35793824394328</v>
       </c>
       <c r="C43">
         <v>221.20000756679073</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.6864084064478551</v>
+        <v>-8.5827149880584717</v>
       </c>
       <c r="B44">
-        <v>-7.6869691638536874</v>
+        <v>-7.7959416645818882</v>
       </c>
       <c r="C44">
         <v>221.20000756679073</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.4830609653733724</v>
+        <v>-8.3785501352644118</v>
       </c>
       <c r="B45">
-        <v>-7.1249768114106766</v>
+        <v>-7.2369539157696874</v>
       </c>
       <c r="C45">
         <v>221.20000756679073</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.2725937669054659</v>
+        <v>-8.16808222802462</v>
       </c>
       <c r="B46">
-        <v>-6.5683884240971118</v>
+        <v>-6.6826415858117958</v>
       </c>
       <c r="C46">
         <v>221.20000756679073</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.0534706573755983</v>
+        <v>-7.9493942876593744</v>
       </c>
       <c r="B47">
-        <v>-6.0183699574925935</v>
+        <v>-6.1344266326398245</v>
       </c>
       <c r="C47">
         <v>221.20000756679073</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.8252353724380459</v>
+        <v>-7.7218885059087983</v>
       </c>
       <c r="B48">
-        <v>-5.4752677206745082</v>
+        <v>-5.5927524926913845</v>
       </c>
       <c r="C48">
         <v>221.20000756679073</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.5877016200777838</v>
+        <v>-7.4852968671179756</v>
       </c>
       <c r="B49">
-        <v>-4.9392231110946758</v>
+        <v>-5.0578179720305849</v>
       </c>
       <c r="C49">
         <v>221.20000756679073</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.340683108279797</v>
+        <v>-7.2393513556319942</v>
       </c>
       <c r="B50">
-        <v>-4.4103775262049272</v>
+        <v>-4.5298218767215372</v>
       </c>
       <c r="C50">
         <v>221.20000756679073</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.0840969269635146</v>
+        <v>-6.9839116663547971</v>
       </c>
       <c r="B51">
-        <v>-3.8887938955630434</v>
+        <v>-4.008868280923382</v>
       </c>
       <c r="C51">
         <v>221.20000756679073</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.8182736937861605</v>
+        <v>-6.7193483364257638</v>
       </c>
       <c r="B52">
-        <v>-3.3742212771506255</v>
+        <v>-3.4946823311753774</v>
       </c>
       <c r="C52">
         <v>221.20000756679073</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.5436474083394129</v>
+        <v>-6.44615961354313</v>
       </c>
       <c r="B53">
-        <v>-2.8663302610552313</v>
+        <v>-2.9868944421118107</v>
       </c>
       <c r="C53">
         <v>221.20000756679073</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.2606520702149409</v>
+        <v>-6.1648437454051273</v>
       </c>
       <c r="B54">
-        <v>-2.3647914373644068</v>
+        <v>-2.4851350283669613</v>
       </c>
       <c r="C54">
         <v>221.20000756679073</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.9696398331553526</v>
+        <v>-5.8758019091451459</v>
       </c>
       <c r="B55">
-        <v>-1.8693375179614271</v>
+        <v>-1.9891065086412363</v>
       </c>
       <c r="C55">
         <v>221.20000756679073</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.670635467506977</v>
+        <v>-5.5790469996371961</v>
       </c>
       <c r="B56">
-        <v>-1.3799497019124427</v>
+        <v>-1.4987993178995329</v>
       </c>
       <c r="C56">
         <v>221.20000756679073</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.3635818977670748</v>
+        <v>-5.2744948411904389</v>
       </c>
       <c r="B57">
-        <v>-0.896671310079315</v>
+        <v>-1.0142758951728623</v>
       </c>
       <c r="C57">
         <v>221.20000756679073</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.0484220484329088</v>
+        <v>-4.9620612581140389</v>
       </c>
       <c r="B58">
-        <v>-0.41954566332391263</v>
+        <v>-0.53559867949224027</v>
       </c>
       <c r="C58">
         <v>221.20000756679073</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.7251063062997147</v>
+        <v>-4.6416728012376733</v>
       </c>
       <c r="B59">
-        <v>0.051389581448672408</v>
+        <v>-0.062822153273877662</v>
       </c>
       <c r="C59">
         <v>221.20000756679073</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.3936149073546495</v>
+        <v>-4.3132989274731113</v>
       </c>
       <c r="B60">
-        <v>0.5161194231604056</v>
+        <v>0.40403102752520803</v>
       </c>
       <c r="C60">
         <v>221.20000756679073</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.0539355498828513</v>
+        <v>-3.9769198202526406</v>
       </c>
       <c r="B61">
-        <v>0.97463452469002221</v>
+        <v>0.86494616356279841</v>
       </c>
       <c r="C61">
         <v>221.20000756679073</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.7060559321694533</v>
+        <v>-3.6325156630085473</v>
       </c>
       <c r="B62">
-        <v>1.4269255489162582</v>
+        <v>1.3199085554966759</v>
       </c>
       <c r="C62">
         <v>221.20000756679073</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.350052089453377</v>
+        <v>-3.2801752041711589</v>
       </c>
       <c r="B63">
-        <v>1.873050207325194</v>
+        <v>1.7689840342803886</v>
       </c>
       <c r="C63">
         <v>221.20000756679073</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.9863534047886664</v>
+        <v>-2.9204214521629583</v>
       </c>
       <c r="B64">
-        <v>2.3133344058323044</v>
+        <v>2.2125605520505589</v>
       </c>
       <c r="C64">
         <v>221.20000756679073</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.6154775981831517</v>
+        <v>-2.5538859804044707</v>
       </c>
       <c r="B65">
-        <v>2.7481710989604076</v>
+        <v>2.6511065912395693</v>
       </c>
       <c r="C65">
         <v>221.20000756679073</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2379423896446604</v>
+        <v>-2.18120036231622</v>
       </c>
       <c r="B66">
-        <v>3.1779532412323248</v>
+        <v>3.0850906342798097</v>
       </c>
       <c r="C66">
         <v>221.20000756679073</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.853556911200154</v>
+        <v>-1.8021401961610613</v>
       </c>
       <c r="B67">
-        <v>3.6025359619995712</v>
+        <v>3.5143462266178833</v>
       </c>
       <c r="C67">
         <v>221.20000756679073</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.4592959429531238</v>
+        <v>-1.4130571795711757</v>
       </c>
       <c r="B68">
-        <v>4.0196230899284489</v>
+        <v>3.9361671657572725</v>
       </c>
       <c r="C68">
         <v>221.20000756679073</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-1.0527925831301073</v>
+        <v>-1.0111016412012517</v>
       </c>
       <c r="B69">
-        <v>4.4274181235454133</v>
+        <v>4.3484396500084728</v>
       </c>
       <c r="C69">
         <v>221.20000756679073</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.63714755437333181</v>
+        <v>-0.60004233442669885</v>
       </c>
       <c r="B70">
-        <v>4.8282745415027151</v>
+        <v>4.7539592288531383</v>
       </c>
       <c r="C70">
         <v>221.20000756679073</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.21574049463746278</v>
+        <v>-0.18398722951458879</v>
       </c>
       <c r="B71">
-        <v>5.2247575218883142</v>
+        <v>5.1557730728028011</v>
       </c>
       <c r="C71">
         <v>221.20000756679073</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.21240092128871779</v>
+        <v>0.23821726042204697</v>
       </c>
       <c r="B72">
-        <v>5.6161290604071814</v>
+        <v>5.5530254853173382</v>
       </c>
       <c r="C72">
         <v>221.20000756679073</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.64883590700180171</v>
+        <v>0.66843269634123559</v>
       </c>
       <c r="B73">
-        <v>6.0012056987699749</v>
+        <v>5.9443356156875362</v>
       </c>
       <c r="C73">
         <v>221.20000756679073</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.0931192664739813</v>
+        <v>1.1060909783311947</v>
       </c>
       <c r="B74">
-        <v>6.3803253450930972</v>
+        <v>6.330124863579468</v>
       </c>
       <c r="C74">
         <v>221.20000756679073</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.5442997932773313</v>
+        <v>1.5500094033541831</v>
       </c>
       <c r="B75">
-        <v>6.7542099743095916</v>
+        <v>6.7112705230303851</v>
       </c>
       <c r="C75">
         <v>221.20000756679073</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.0014066490078619</v>
+        <v>1.9989765167384341</v>
       </c>
       <c r="B76">
-        <v>7.1235964622133379</v>
+        <v>7.0886712151869515</v>
       </c>
       <c r="C76">
         <v>221.20000756679073</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.4635681414138229</v>
+        <v>2.4518980444657204</v>
       </c>
       <c r="B77">
-        <v>7.4891464317040723</v>
+        <v>7.4631386400623372</v>
       </c>
       <c r="C77">
         <v>221.20000756679073</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.9303287948284886</v>
+        <v>2.90817718676601</v>
       </c>
       <c r="B78">
-        <v>7.8512055932441411</v>
+        <v>7.8351154860262922</v>
       </c>
       <c r="C78">
         <v>221.20000756679073</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.4007682034220026</v>
+        <v>3.36665163843461</v>
       </c>
       <c r="B79">
-        <v>8.2104725438130011</v>
+        <v>8.2054639166084691</v>
       </c>
       <c r="C79">
         <v>221.20000756679073</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.8731225178289796</v>
+        <v>3.825132147138433</v>
       </c>
       <c r="B80">
-        <v>8.5682860622394</v>
+        <v>8.5758078542615532</v>
       </c>
       <c r="C80">
         <v>221.20000756679073</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.342692448265181</v>
+        <v>4.2778721621184186</v>
       </c>
       <c r="B81">
-        <v>8.92821295518878</v>
+        <v>8.9504099199096512</v>
       </c>
       <c r="C81">
         <v>221.20000756679073</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.7198189463968845</v>
+        <v>4.6163197893269912</v>
       </c>
       <c r="B82">
-        <v>9.3583053126357765</v>
+        <v>9.4097906891674281</v>
       </c>
       <c r="C82">
         <v>221.20000756679073</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.8165578624391348</v>
+        <v>4.7085362436532785</v>
       </c>
       <c r="B1">
-        <v>10.2996316704634</v>
+        <v>10.34946030629812</v>
       </c>
       <c r="C1">
         <v>245.30998079303629</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3.97640203529279</v>
+        <v>3.7948726704971278</v>
       </c>
       <c r="B2">
-        <v>10.137002371493059</v>
+        <v>10.230344328973732</v>
       </c>
       <c r="C2">
         <v>245.30998079303629</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.3120175177853466</v>
+        <v>3.1050576850436959</v>
       </c>
       <c r="B3">
-        <v>9.8494835377209426</v>
+        <v>9.95567729970495</v>
       </c>
       <c r="C3">
         <v>245.30998079303629</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2.6831300117854155</v>
+        <v>2.4575102014920036</v>
       </c>
       <c r="B4">
-        <v>9.5367432655745326</v>
+        <v>9.6516388348092939</v>
       </c>
       <c r="C4">
         <v>245.30998079303629</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.0816441432990689</v>
+        <v>1.8418377932205108</v>
       </c>
       <c r="B5">
-        <v>9.2045335033907048</v>
+        <v>9.3254505697226868</v>
       </c>
       <c r="C5">
         <v>245.30998079303629</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.5040999662827479</v>
+        <v>1.2536434987752894</v>
       </c>
       <c r="B6">
-        <v>8.8553126219508282</v>
+        <v>8.9801679268024284</v>
       </c>
       <c r="C6">
         <v>245.30998079303629</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>0.94843215567212225</v>
+        <v>0.69032692740180746</v>
       </c>
       <c r="B7">
-        <v>8.4905480819402</v>
+        <v>8.6175979021144151</v>
       </c>
       <c r="C7">
         <v>245.30998079303629</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.41333666436220134</v>
+        <v>0.15026919654450524</v>
       </c>
       <c r="B8">
-        <v>8.11116643864613</v>
+        <v>8.23886544751595</v>
       </c>
       <c r="C8">
         <v>245.30998079303629</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-0.1030578517047325</v>
+        <v>-0.36889270277817249</v>
       </c>
       <c r="B9">
-        <v>7.7184973248130131</v>
+        <v>7.8456126038910394</v>
       </c>
       <c r="C9">
         <v>245.30998079303629</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.60274065473170813</v>
+        <v>-0.8696787598078729</v>
       </c>
       <c r="B10">
-        <v>7.3139541567238915</v>
+        <v>7.4395904967725732</v>
       </c>
       <c r="C10">
         <v>245.30998079303629</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-1.0876053825502643</v>
+        <v>-1.3544927584005864</v>
       </c>
       <c r="B11">
-        <v>6.8988824073592543</v>
+        <v>7.0224695012622327</v>
       </c>
       <c r="C11">
         <v>245.30998079303629</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-1.5587283710167657</v>
+        <v>-1.8246835028281443</v>
       </c>
       <c r="B12">
-        <v>6.4740468379572542</v>
+        <v>6.5951868934246285</v>
       </c>
       <c r="C12">
         <v>245.30998079303629</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-2.0140123724583621</v>
+        <v>-2.2774960844113643</v>
       </c>
       <c r="B13">
-        <v>6.03795730608928</v>
+        <v>6.1558283036072448</v>
       </c>
       <c r="C13">
         <v>245.30998079303629</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.452244664375427</v>
+        <v>-2.7113245249389206</v>
       </c>
       <c r="B14">
-        <v>5.5897521446884264</v>
+        <v>5.7032777471048126</v>
       </c>
       <c r="C14">
         <v>245.30998079303629</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.8789242084904538</v>
+        <v>-3.1332622810218838</v>
       </c>
       <c r="B15">
-        <v>5.1333384918014309</v>
+        <v>5.242464424718186</v>
       </c>
       <c r="C15">
         <v>245.30998079303629</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.2990936363378882</v>
+        <v>-3.549814440088686</v>
       </c>
       <c r="B16">
-        <v>4.672299252441678</v>
+        <v>4.7779086830033446</v>
       </c>
       <c r="C16">
         <v>245.30998079303629</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.709258574477909</v>
+        <v>-3.9564331780148092</v>
       </c>
       <c r="B17">
-        <v>4.2041515943755066</v>
+        <v>4.3064502660306543</v>
       </c>
       <c r="C17">
         <v>245.30998079303629</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-4.1048738697784835</v>
+        <v>-4.3472129090254361</v>
       </c>
       <c r="B18">
-        <v>3.7256660823701298</v>
+        <v>3.8239854173768677</v>
       </c>
       <c r="C18">
         <v>245.30998079303629</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.4857282553130533</v>
+        <v>-4.7218699122975591</v>
       </c>
       <c r="B19">
-        <v>3.2366926064432553</v>
+        <v>3.3303169811299029</v>
       </c>
       <c r="C19">
         <v>245.30998079303629</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.85269393570643</v>
+        <v>-5.0815259332461276</v>
       </c>
       <c r="B20">
-        <v>2.7378508879252164</v>
+        <v>2.8262244515054626</v>
       </c>
       <c r="C20">
         <v>245.30998079303629</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-5.2066431155834154</v>
+        <v>-5.4273027172860822</v>
       </c>
       <c r="B21">
-        <v>2.2297606481463523</v>
+        <v>2.3124873227192606</v>
       </c>
       <c r="C21">
         <v>245.30998079303629</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.5482887032156842</v>
+        <v>-5.7601182790066012</v>
       </c>
       <c r="B22">
-        <v>1.7129284247355159</v>
+        <v>1.7897435176481427</v>
       </c>
       <c r="C22">
         <v>245.30998079303629</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.8777064214623538</v>
+        <v>-6.0800757096937863</v>
       </c>
       <c r="B23">
-        <v>1.187408020515637</v>
+        <v>1.2580646738135424</v>
       </c>
       <c r="C23">
         <v>245.30998079303629</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.1948126968293993</v>
+        <v>-6.3870743698079648</v>
       </c>
       <c r="B24">
-        <v>0.65314005460816993</v>
+        <v>0.71738085739804025</v>
       </c>
       <c r="C24">
         <v>245.30998079303629</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.4995239558227995</v>
+        <v>-6.6810136198094687</v>
       </c>
       <c r="B25">
-        <v>0.11006514613456356</v>
+        <v>0.16762213458421149</v>
       </c>
       <c r="C25">
         <v>245.30998079303629</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.791722851286786</v>
+        <v>-6.961751691256346</v>
       </c>
       <c r="B26">
-        <v>-0.44190008274269232</v>
+        <v>-0.39131000867489041</v>
       </c>
       <c r="C26">
         <v>245.30998079303629</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.0711569414186046</v>
+        <v>-7.228982300097508</v>
       </c>
       <c r="B27">
-        <v>-1.0029349976969606</v>
+        <v>-0.959628407344322</v>
       </c>
       <c r="C27">
         <v>245.30998079303629</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.3375400107537523</v>
+        <v>-7.4823580333795814</v>
       </c>
       <c r="B28">
-        <v>-1.57324296136056</v>
+        <v>-1.5375744766186559</v>
       </c>
       <c r="C28">
         <v>245.30998079303629</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.5905858438277223</v>
+        <v>-7.7215314781491946</v>
       </c>
       <c r="B29">
-        <v>-2.1530273363658146</v>
+        <v>-2.1253896316924723</v>
       </c>
       <c r="C29">
         <v>245.30998079303629</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.8301098949238748</v>
+        <v>-7.9462899172606791</v>
       </c>
       <c r="B30">
-        <v>-2.7424192466643436</v>
+        <v>-2.7232216884448652</v>
       </c>
       <c r="C30">
         <v>245.30998079303629</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-8.056334297316992</v>
+        <v>-8.1569594167991788</v>
       </c>
       <c r="B31">
-        <v>-3.3412608614849613</v>
+        <v>-3.3308440654929941</v>
       </c>
       <c r="C31">
         <v>245.30998079303629</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.2695828540297285</v>
+        <v>-8.3540007386575432</v>
       </c>
       <c r="B32">
-        <v>-3.9493221113757886</v>
+        <v>-3.9479365821385475</v>
       </c>
       <c r="C32">
         <v>245.30998079303629</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.470179368084727</v>
+        <v>-8.5378746447286264</v>
       </c>
       <c r="B33">
-        <v>-4.56637292688494</v>
+        <v>-4.5741790576832031</v>
       </c>
       <c r="C33">
         <v>245.30998079303629</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.6582527625077965</v>
+        <v>-8.7087934977117438</v>
       </c>
       <c r="B34">
-        <v>-5.1923217052545318</v>
+        <v>-5.209423922550517</v>
       </c>
       <c r="C34">
         <v>245.30998079303629</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.83315244033739</v>
+        <v>-8.8659760635321039</v>
       </c>
       <c r="B35">
-        <v>-5.827630710502727</v>
+        <v>-5.8542140516515957</v>
       </c>
       <c r="C35">
         <v>245.30998079303629</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.9940329246151283</v>
+        <v>-9.0083927089213844</v>
       </c>
       <c r="B36">
-        <v>-6.47290067334169</v>
+        <v>-6.5092649310194188</v>
       </c>
       <c r="C36">
         <v>245.30998079303629</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-9.14004873838263</v>
+        <v>-9.1350138006112633</v>
       </c>
       <c r="B37">
-        <v>-7.1287323244835932</v>
+        <v>-7.175292046686975</v>
       </c>
       <c r="C37">
         <v>245.30998079303629</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-9.26989392200676</v>
+        <v>-9.2442180561673055</v>
       </c>
       <c r="B38">
-        <v>-7.7960535781107163</v>
+        <v>-7.8534220181731236</v>
       </c>
       <c r="C38">
         <v>245.30998079303629</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.3804205851553828</v>
+        <v>-9.3320175964906049</v>
       </c>
       <c r="B39">
-        <v>-8.4771010822857917</v>
+        <v>-8.54642599894025</v>
       </c>
       <c r="C39">
         <v>245.30998079303629</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.4680203548216042</v>
+        <v>-9.39383289331614</v>
       </c>
       <c r="B40">
-        <v>-9.1744386685416615</v>
+        <v>-9.257486275936607</v>
       </c>
       <c r="C40">
         <v>245.30998079303629</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.5290848579985337</v>
+        <v>-9.425084418378896</v>
       </c>
       <c r="B41">
-        <v>-9.89063016841117</v>
+        <v>-9.989785136110461</v>
       </c>
       <c r="C41">
         <v>245.30998079303629</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.5290848579985337</v>
+        <v>-9.425084418378896</v>
       </c>
       <c r="B42">
-        <v>-9.89063016841117</v>
+        <v>-9.989785136110461</v>
       </c>
       <c r="C42">
         <v>245.30998079303629</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.3129483294902844</v>
+        <v>-9.1929833657658264</v>
       </c>
       <c r="B43">
-        <v>-9.2846208885193384</v>
+        <v>-9.397055417799935</v>
       </c>
       <c r="C43">
         <v>245.30998079303629</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-9.0969089284139066</v>
+        <v>-8.964812859273362</v>
       </c>
       <c r="B44">
-        <v>-8.6785425973661781</v>
+        <v>-8.80159438637258</v>
       </c>
       <c r="C44">
         <v>245.30998079303629</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.87801175412297</v>
+        <v>-8.7366516649585328</v>
       </c>
       <c r="B45">
-        <v>-8.0744948194296953</v>
+        <v>-8.2061268839683752</v>
       </c>
       <c r="C45">
         <v>245.30998079303629</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.6533019059710412</v>
+        <v>-8.5045785488783689</v>
       </c>
       <c r="B46">
-        <v>-7.4745770791879051</v>
+        <v>-7.6133777527273239</v>
       </c>
       <c r="C46">
         <v>245.30998079303629</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.4202518295443269</v>
+        <v>-8.2652305453006445</v>
       </c>
       <c r="B47">
-        <v>-6.8805852618485428</v>
+        <v>-7.0256838975308327</v>
       </c>
       <c r="C47">
         <v>245.30998079303629</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.1780433553595877</v>
+        <v>-8.0174777613361581</v>
       </c>
       <c r="B48">
-        <v>-6.2931006955382562</v>
+        <v>-6.443830474226008</v>
       </c>
       <c r="C48">
         <v>245.30998079303629</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.9262856601662239</v>
+        <v>-7.76074857230645</v>
       </c>
       <c r="B49">
-        <v>-5.7124010691134171</v>
+        <v>-5.8682147014013708</v>
       </c>
       <c r="C49">
         <v>245.30998079303629</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.6645879207136325</v>
+        <v>-7.4944713535330667</v>
       </c>
       <c r="B50">
-        <v>-5.1387640714304021</v>
+        <v>-5.2992337976454529</v>
       </c>
       <c r="C50">
         <v>245.30998079303629</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.392726331579623</v>
+        <v>-7.2182948117681809</v>
       </c>
       <c r="B51">
-        <v>-4.572348721359357</v>
+        <v>-4.73713187454636</v>
       </c>
       <c r="C51">
         <v>245.30998079303629</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.1111451586556482</v>
+        <v>-6.9327489794864734</v>
       </c>
       <c r="B52">
-        <v>-4.0128393578255359</v>
+        <v>-4.1815406156905475</v>
       </c>
       <c r="C52">
         <v>245.30998079303629</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.8204556856615719</v>
+        <v>-6.6385842205932537</v>
       </c>
       <c r="B53">
-        <v>-3.4598016497679556</v>
+        <v>-3.6319385976640488</v>
       </c>
       <c r="C53">
         <v>245.30998079303629</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.521269196317248</v>
+        <v>-6.3365508989938251</v>
       </c>
       <c r="B54">
-        <v>-2.9128012661256339</v>
+        <v>-3.0878043970528908</v>
       </c>
       <c r="C54">
         <v>245.30998079303629</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.2140743681355417</v>
+        <v>-6.0272435918368732</v>
       </c>
       <c r="B55">
-        <v>-2.3714909903512589</v>
+        <v>-2.5487248457335294</v>
       </c>
       <c r="C55">
         <v>245.30998079303629</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.8988694538013267</v>
+        <v>-5.7106337292445826</v>
       </c>
       <c r="B56">
-        <v>-1.8358720639521839</v>
+        <v>-2.0147197967440982</v>
       </c>
       <c r="C56">
         <v>245.30998079303629</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.5755300997924753</v>
+        <v>-5.3865369545825184</v>
       </c>
       <c r="B57">
-        <v>-1.3060328429494281</v>
+        <v>-1.4859173584131467</v>
       </c>
       <c r="C57">
         <v>245.30998079303629</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.2439319525868671</v>
+        <v>-5.0547689112162475</v>
       </c>
       <c r="B58">
-        <v>-0.78206168336401483</v>
+        <v>-0.96244563906923253</v>
       </c>
       <c r="C58">
         <v>245.30998079303629</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.9039662628193037</v>
+        <v>-4.71516806783633</v>
       </c>
       <c r="B59">
-        <v>-0.26403585410664537</v>
+        <v>-0.44441688585834976</v>
       </c>
       <c r="C59">
         <v>245.30998079303629</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.5555866977523127</v>
+        <v>-4.3676641944333054</v>
       </c>
       <c r="B60">
-        <v>0.24801172435322738</v>
+        <v>0.068120098803720053</v>
       </c>
       <c r="C60">
         <v>245.30998079303629</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.1987625288053518</v>
+        <v>-4.0122098863227178</v>
       </c>
       <c r="B61">
-        <v>0.7540592186564713</v>
+        <v>0.5751323736837527</v>
       </c>
       <c r="C61">
         <v>245.30998079303629</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.8334630273978783</v>
+        <v>-3.6487577388201071</v>
       </c>
       <c r="B62">
-        <v>1.254084795443946</v>
+        <v>1.0765869975485192</v>
       </c>
       <c r="C62">
         <v>245.30998079303629</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.4597987637025489</v>
+        <v>-3.2774459476628537</v>
       </c>
       <c r="B63">
-        <v>1.7481670173516943</v>
+        <v>1.5725800017938141</v>
       </c>
       <c r="C63">
         <v>245.30998079303629</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-3.0784455029048075</v>
+        <v>-2.8991551102756996</v>
       </c>
       <c r="B64">
-        <v>2.2367860309964773</v>
+        <v>2.0637233083315212</v>
       </c>
       <c r="C64">
         <v>245.30998079303629</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.690220308943307</v>
+        <v>-2.5149514245052336</v>
       </c>
       <c r="B65">
-        <v>2.7205223789902235</v>
+        <v>2.550757811702534</v>
       </c>
       <c r="C65">
         <v>245.30998079303629</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2959402457566882</v>
+        <v>-2.1259010881980376</v>
       </c>
       <c r="B66">
-        <v>3.1999566039448704</v>
+        <v>3.0344244064477581</v>
       </c>
       <c r="C66">
         <v>245.30998079303629</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.8953239506478716</v>
+        <v>-1.7316497675250668</v>
       </c>
       <c r="B67">
-        <v>3.6748887912303161</v>
+        <v>3.5144768680972822</v>
       </c>
       <c r="C67">
         <v>245.30998079303629</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.4836963543768649</v>
+        <v>-1.3261610019547656</v>
       </c>
       <c r="B68">
-        <v>4.1419971972483056</v>
+        <v>3.9867204961379503</v>
       </c>
       <c r="C68">
         <v>245.30998079303629</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-1.0574108631293295</v>
+        <v>-0.904733623756505</v>
       </c>
       <c r="B69">
-        <v>4.5986908337083268</v>
+        <v>4.4478884770804763</v>
       </c>
       <c r="C69">
         <v>245.30998079303629</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.62132849133647239</v>
+        <v>-0.47368976310591721</v>
       </c>
       <c r="B70">
-        <v>5.0484235625189307</v>
+        <v>4.90237402157426</v>
       </c>
       <c r="C70">
         <v>245.30998079303629</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.18074802785109437</v>
+        <v>-0.039921226672135109</v>
       </c>
       <c r="B71">
-        <v>5.494960294325649</v>
+        <v>5.354966205075093</v>
       </c>
       <c r="C71">
         <v>245.30998079303629</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.26578824903317544</v>
+        <v>0.398424770807954</v>
       </c>
       <c r="B72">
-        <v>5.9372652845228764</v>
+        <v>5.804377538125653</v>
       </c>
       <c r="C72">
         <v>245.30998079303629</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.72064546204356728</v>
+        <v>0.84437298971344132</v>
       </c>
       <c r="B73">
-        <v>6.3736580593304506</v>
+        <v>6.2485061327324667</v>
       </c>
       <c r="C73">
         <v>245.30998079303629</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.1830618274315776</v>
+        <v>1.2968914989550895</v>
       </c>
       <c r="B74">
-        <v>6.8046798835211328</v>
+        <v>6.6880690716706059</v>
       </c>
       <c r="C74">
         <v>245.30998079303629</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.6514832137419551</v>
+        <v>1.7539185262650507</v>
       </c>
       <c r="B75">
-        <v>7.2314350030316836</v>
+        <v>7.1244990682237441</v>
       </c>
       <c r="C75">
         <v>245.30998079303629</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.1243130051681769</v>
+        <v>2.213329626129362</v>
       </c>
       <c r="B76">
-        <v>7.6550578499019126</v>
+        <v>7.5592723869414469</v>
       </c>
       <c r="C76">
         <v>245.30998079303629</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.6001020534729968</v>
+        <v>2.6731871007628154</v>
       </c>
       <c r="B77">
-        <v>8.0765780770915683</v>
+        <v>7.9937355224875049</v>
       </c>
       <c r="C77">
         <v>245.30998079303629</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.0780335650475292</v>
+        <v>3.1323629165413345</v>
       </c>
       <c r="B78">
-        <v>8.4965760351371049</v>
+        <v>8.4286723387167459</v>
       </c>
       <c r="C78">
         <v>245.30998079303629</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.5565607389351297</v>
+        <v>3.5887790329987688</v>
       </c>
       <c r="B79">
-        <v>8.9161507614884</v>
+        <v>8.865526853587065</v>
       </c>
       <c r="C79">
         <v>245.30998079303629</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>4.032809865433169</v>
+        <v>4.03862905085025</v>
       </c>
       <c r="B80">
-        <v>9.3373440926013185</v>
+        <v>9.306944111317673</v>
       </c>
       <c r="C80">
         <v>245.30998079303629</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.4993298169196407</v>
+        <v>4.4721695437293336</v>
       </c>
       <c r="B81">
-        <v>9.7654502250337227</v>
+        <v>9.7596947609280615</v>
       </c>
       <c r="C81">
         <v>245.30998079303629</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.8165578624391348</v>
+        <v>4.7085362436532785</v>
       </c>
       <c r="B82">
-        <v>10.2996316704634</v>
+        <v>10.34946030629812</v>
       </c>
       <c r="C82">
         <v>245.30998079303629</v>
